--- a/data/trans_bre/P16A11-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 7,75</t>
+          <t>-3,19; 8,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 10,11</t>
+          <t>-1,92; 9,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 7,66</t>
+          <t>-3,62; 7,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,25</t>
+          <t>-6,77; 3,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 78,03</t>
+          <t>-24,01; 81,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 107,47</t>
+          <t>-13,25; 104,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 96,43</t>
+          <t>-28,2; 98,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 25,65</t>
+          <t>-29,41; 23,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,95</t>
+          <t>2,55; 11,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,26</t>
+          <t>-0,26; 9,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,85</t>
+          <t>1,46; 11,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 3,95</t>
+          <t>-4,25; 4,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,93; 119,09</t>
+          <t>20,77; 136,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 69,87</t>
+          <t>-3,59; 69,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 85,51</t>
+          <t>7,67; 83,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 32,18</t>
+          <t>-24,22; 32,91</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 11,36</t>
+          <t>-0,02; 11,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 11,06</t>
+          <t>-1,95; 10,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 5,87</t>
+          <t>-5,26; 5,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,34</t>
+          <t>-3,1; 7,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 103,33</t>
+          <t>-0,91; 105,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 74,09</t>
+          <t>-9,56; 70,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 47,61</t>
+          <t>-28,8; 43,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 38,69</t>
+          <t>-13,15; 41,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 10,54</t>
+          <t>-0,08; 10,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 11,8</t>
+          <t>0,2; 12,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 10,73</t>
+          <t>-0,61; 10,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 4,34</t>
+          <t>-10,02; 4,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 101,76</t>
+          <t>-1,64; 94,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 75,95</t>
+          <t>1,06; 84,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 74,93</t>
+          <t>-3,72; 75,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,86; 25,81</t>
+          <t>-44,19; 23,22</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 8,97</t>
+          <t>-3,0; 9,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 19,21</t>
+          <t>2,53; 18,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 15,76</t>
+          <t>1,61; 15,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 13,07</t>
+          <t>1,28; 13,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 141,56</t>
+          <t>-28,16; 160,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 167,7</t>
+          <t>9,56; 147,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 193,85</t>
+          <t>11,06; 192,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 87,15</t>
+          <t>5,74; 82,21</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 9,96</t>
+          <t>-2,17; 10,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 6,76</t>
+          <t>-6,99; 7,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 9,35</t>
+          <t>-3,05; 9,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 1,63</t>
+          <t>-10,12; 1,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 77,61</t>
+          <t>-11,7; 89,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 36,05</t>
+          <t>-26,93; 37,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 82,45</t>
+          <t>-19,0; 86,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 7,5</t>
+          <t>-31,37; 6,62</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,62</t>
+          <t>-0,25; 8,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 9,24</t>
+          <t>0,52; 9,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 3,18</t>
+          <t>-4,73; 3,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 48,4</t>
+          <t>0,41; 53,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 68,85</t>
+          <t>-1,67; 64,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 57,02</t>
+          <t>2,61; 56,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 24,87</t>
+          <t>-27,46; 24,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 327,33</t>
+          <t>2,09; 374,43</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 4,92</t>
+          <t>-1,92; 4,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 5,99</t>
+          <t>-1,35; 6,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,44</t>
+          <t>-1,43; 6,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 17,06</t>
+          <t>2,99; 17,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 49,54</t>
+          <t>-14,81; 47,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 48,35</t>
+          <t>-8,23; 50,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 45,82</t>
+          <t>-8,35; 45,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,8; 257,17</t>
+          <t>14,99; 250,13</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,65</t>
+          <t>2,25; 5,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,22</t>
+          <t>2,19; 6,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,68</t>
+          <t>1,14; 4,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 23,27</t>
+          <t>1,21; 21,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,1; 47,7</t>
+          <t>16,41; 48,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,74; 39,26</t>
+          <t>11,94; 38,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,09; 33,25</t>
+          <t>7,41; 33,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,5; 150,83</t>
+          <t>6,66; 131,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A11-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>-3,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-4,66%</t>
+          <t>-16,42%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 8,39</t>
+          <t>-3,08; 8,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 9,83</t>
+          <t>-2,8; 9,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 7,45</t>
+          <t>-3,45; 8,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 3,94</t>
+          <t>-8,58; 2,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 81,6</t>
+          <t>-22,2; 86,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 104,81</t>
+          <t>-19,14; 101,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 98,15</t>
+          <t>-27,04; 108,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 23,61</t>
+          <t>-35,56; 12,77</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,12%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,96</t>
+          <t>2,81; 11,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,74</t>
+          <t>-0,15; 9,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 11,23</t>
+          <t>1,81; 11,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,05</t>
+          <t>-4,29; 4,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,77; 136,3</t>
+          <t>22,32; 124,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 69,85</t>
+          <t>-1,33; 70,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 83,35</t>
+          <t>9,15; 84,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 32,91</t>
+          <t>-24,13; 34,61</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 11,78</t>
+          <t>0,01; 12,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 10,78</t>
+          <t>-1,72; 11,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,5</t>
+          <t>-5,1; 6,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 7,97</t>
+          <t>-3,25; 7,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 105,17</t>
+          <t>-1,34; 113,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 70,14</t>
+          <t>-8,29; 77,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 43,43</t>
+          <t>-28,42; 48,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 41,61</t>
+          <t>-12,46; 40,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,46</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,38%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 10,2</t>
+          <t>-0,43; 10,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 12,65</t>
+          <t>0,26; 12,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 10,81</t>
+          <t>-1,0; 11,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 4,17</t>
+          <t>-3,02; 7,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 94,17</t>
+          <t>-2,96; 90,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 84,48</t>
+          <t>0,67; 83,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 75,68</t>
+          <t>-5,69; 76,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 23,22</t>
+          <t>-13,49; 50,49</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 9,33</t>
+          <t>-2,86; 9,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 18,4</t>
+          <t>2,69; 18,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 15,04</t>
+          <t>1,63; 15,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 13,04</t>
+          <t>1,35; 13,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 160,77</t>
+          <t>-27,25; 154,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 147,54</t>
+          <t>10,22; 158,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 192,44</t>
+          <t>7,22; 184,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 82,21</t>
+          <t>6,7; 92,54</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,88</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-14,16%</t>
+          <t>-11,97%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 10,34</t>
+          <t>-2,42; 10,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 7,35</t>
+          <t>-6,46; 7,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 9,3</t>
+          <t>-3,17; 9,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 1,54</t>
+          <t>-9,14; 2,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 89,74</t>
+          <t>-14,69; 82,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 37,78</t>
+          <t>-24,72; 37,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 86,47</t>
+          <t>-18,41; 81,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 6,62</t>
+          <t>-30,13; 9,62</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,24</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>120,14%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 8,16</t>
+          <t>-0,15; 8,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 9,16</t>
+          <t>0,02; 9,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 3,29</t>
+          <t>-4,53; 3,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 53,22</t>
+          <t>-1,59; 6,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 64,76</t>
+          <t>-0,82; 65,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 56,31</t>
+          <t>-0,12; 56,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 24,71</t>
+          <t>-26,32; 31,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 374,43</t>
+          <t>-8,09; 38,52</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,84</t>
+          <t>-1,77; 5,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,15</t>
+          <t>-1,09; 6,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,58</t>
+          <t>-1,36; 6,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,39</t>
+          <t>0,04; 7,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 47,97</t>
+          <t>-14,31; 48,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 50,74</t>
+          <t>-6,93; 53,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 45,78</t>
+          <t>-7,95; 43,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,99; 250,13</t>
+          <t>-0,07; 45,17</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,83</t>
+          <t>2,31; 5,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,17</t>
+          <t>2,18; 6,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,7</t>
+          <t>1,03; 4,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 21,93</t>
+          <t>0,1; 3,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,41; 48,5</t>
+          <t>17,09; 48,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,94; 38,67</t>
+          <t>12,42; 39,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 33,89</t>
+          <t>6,48; 34,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,66; 131,33</t>
+          <t>0,52; 19,23</t>
         </is>
       </c>
     </row>
